--- a/314e-ig/output/StructureDefinition-procedure-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-procedure-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-procedure-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-procedure-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-procedure-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-procedure-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-procedure-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-procedure-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -581,7 +581,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-careplan|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-servicerequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -604,7 +604,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure|Observation|MedicationAdministration) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/procedure-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/medicationadministration-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -867,7 +867,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -892,7 +892,7 @@
     <t>Procedure.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -948,7 +948,7 @@
     <t>Procedure.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson|Practitioner|PractitionerRole) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1051,7 +1051,7 @@
     <t>Procedure.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-practitioner|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-organization|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-relatedperson) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1079,7 +1079,7 @@
     <t>Procedure.performer.onBehalfOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1098,7 +1098,7 @@
     <t>Procedure.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/location-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1147,7 +1147,7 @@
     <t>Procedure.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-condition-encounter-diagnosis|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-condition-problems-health-concerns|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-diagnosticreport-note|http://hl7.org/fhir/us/core/StructureDefinition/us-core-documentreference) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1212,7 +1212,7 @@
     <t>Procedure.report</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DiagnosticReport|DocumentReference|Composition) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1252,7 +1252,7 @@
     <t>Procedure.complicationDetail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1347,7 +1347,7 @@
     <t>Procedure.focalDevice.manipulated</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/device-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1363,7 +1363,7 @@
     <t>Procedure.usedReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Medication|Substance) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/medication-314e|http://314e.com/fhir/StructureDefinition/substance-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-procedure-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-procedure-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-procedure-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-procedure-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
